--- a/Documentation/T24Res/T24RCustomStdDesign.xlsx
+++ b/Documentation/T24Res/T24RCustomStdDesign.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\svn-CEC\SF_CBECC-Com\branches\CBECC-Com_MFamRestructure\RulesetDev\Rulesets\shared\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CBECC\SVN\branches\CBECC-Com_MFamRestructure\Documentation\T24Res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CFAB4B-E439-4FFB-96E8-C3AF61DCA875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71481180-D713-48D8-97D8-A5E088BA1223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="1350" windowWidth="26070" windowHeight="14040" xr2:uid="{07D8E957-2C9A-4D7E-8925-FE375302CA45}"/>
+    <workbookView xWindow="24549" yWindow="2571" windowWidth="22868" windowHeight="14615" xr2:uid="{07D8E957-2C9A-4D7E-8925-FE375302CA45}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,42 +33,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Scott Criswell</author>
-  </authors>
-  <commentList>
-    <comment ref="D65" authorId="0" shapeId="0" xr:uid="{48D16B95-9F7F-4D68-96F2-5CE946FAFC49}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>SAC 12/03/21:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-switched from MultiFam to '*' to handle both LowRiseRes &amp; HiRiseRes</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="67">
   <si>
     <t>;</t>
   </si>
@@ -241,14 +207,41 @@
     <t>2022 Final</t>
   </si>
   <si>
-    <t>12/03/21 - SAC - switched BldgType records for MultiFam to '*' to handle both LowRiseRes &amp; HiRiseRes</t>
+    <t>2025 Final</t>
+  </si>
+  <si>
+    <t>All SFam models</t>
+  </si>
+  <si>
+    <t>03/10/25-03/11/25 - SAC - added '2025 Final' record to implement HP HVAC &amp; DHW Std design</t>
+  </si>
+  <si>
+    <t>Lowrise MFam models</t>
+  </si>
+  <si>
+    <t>LowRiseRes</t>
+  </si>
+  <si>
+    <t>HiRiseRes</t>
+  </si>
+  <si>
+    <t>Highrise MFam models</t>
+  </si>
+  <si>
+    <t>SuppHtg</t>
+  </si>
+  <si>
+    <t>05/22/25 - SAC - added '2025 Final' records for HiRise &amp; LowRise MFam zones &amp; SuppHtg column for ElecRes vs. Gas HP supplemental heating</t>
+  </si>
+  <si>
+    <t>default  -or-  Electricity  -or-  Gas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,19 +285,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -320,7 +300,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -357,11 +337,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -412,6 +412,33 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,9 +457,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -470,7 +497,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -576,7 +603,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -718,15 +745,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C373ABC9-0F2E-48ED-B208-F0F9FC7924F4}">
-  <dimension ref="A1:U82"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C373ABC9-0F2E-48ED-B208-F0F9FC7924F4}">
+  <dimension ref="A1:V92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="3.7109375" customWidth="1"/>
@@ -735,16 +762,16 @@
     <col min="5" max="5" width="14.85546875" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" customWidth="1"/>
     <col min="7" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.28515625" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" customWidth="1"/>
+    <col min="9" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -782,7 +809,7 @@
         <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -790,7 +817,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -798,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -806,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -814,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -822,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -830,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -838,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -846,31 +873,28 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="s">
-        <v>29</v>
+      <c r="B15" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -878,356 +902,273 @@
         <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>0</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E21" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="1" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="1" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="1" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E26" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" s="1" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E27" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>0</v>
-      </c>
-      <c r="C26" s="1" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E28" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="1" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E29" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" s="1" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E30" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="5" t="s">
+    <row r="34" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E34" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F34" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G34" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H34" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="J34" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K34" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K32" s="8" t="s">
+      <c r="L34" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L32" s="8" t="s">
+      <c r="M34" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M32" s="8" t="s">
+      <c r="N34" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="N32" s="8" t="s">
+      <c r="O34" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O32" s="8" t="s">
+      <c r="P34" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="P32" s="8" t="s">
+      <c r="Q34" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="Q32" s="8" t="s">
+      <c r="R34" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="R32" s="8" t="s">
+      <c r="S34" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
-      <c r="U32" s="5"/>
-    </row>
-    <row r="33" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C33" t="s">
-        <v>56</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35" t="s">
         <v>36</v>
       </c>
-      <c r="E33" s="2">
-        <v>0</v>
-      </c>
-      <c r="F33" s="15">
+      <c r="E35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="15">
         <v>1</v>
       </c>
-      <c r="G33" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K33" s="7">
+      <c r="G35" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L35" s="26">
         <v>0.7</v>
       </c>
-      <c r="L33" s="9">
-        <v>0</v>
-      </c>
-      <c r="M33" s="9">
-        <v>0</v>
-      </c>
-      <c r="N33" s="9">
-        <v>0</v>
-      </c>
-      <c r="O33" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P33" s="9">
-        <v>-1</v>
-      </c>
-      <c r="Q33" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R33" s="9">
-        <v>-1</v>
-      </c>
-      <c r="S33" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C34" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0</v>
-      </c>
-      <c r="F34" s="15">
-        <f>F33+1</f>
-        <v>2</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K34" s="9">
-        <v>0</v>
-      </c>
-      <c r="L34" s="9">
-        <v>0</v>
-      </c>
-      <c r="M34" s="9">
-        <v>0</v>
-      </c>
-      <c r="N34" s="9">
-        <v>0</v>
-      </c>
-      <c r="O34" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P34" s="9">
-        <v>-1</v>
-      </c>
-      <c r="Q34" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R34" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C35" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0</v>
-      </c>
-      <c r="F35" s="15">
-        <f t="shared" ref="F35:F48" si="0">F34+1</f>
-        <v>3</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K35" s="9">
-        <v>0</v>
-      </c>
-      <c r="L35" s="9">
-        <v>0</v>
-      </c>
       <c r="M35" s="9">
         <v>0</v>
       </c>
       <c r="N35" s="9">
         <v>0</v>
       </c>
-      <c r="O35" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P35" s="9">
-        <v>-1</v>
+      <c r="O35" s="9">
+        <v>0</v>
+      </c>
+      <c r="P35" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q35" s="9">
         <v>-1</v>
@@ -1235,20 +1176,29 @@
       <c r="R35" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="36" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C36" s="20" t="s">
-        <v>56</v>
+      <c r="S35" s="9">
+        <v>-1</v>
+      </c>
+      <c r="T35" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C36" s="20" t="str">
+        <f>C35</f>
+        <v>2025 Final</v>
       </c>
       <c r="D36" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="9">
-        <v>0</v>
+      <c r="E36" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="F36" s="15">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>30</v>
@@ -1260,25 +1210,25 @@
         <v>17</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K36" s="9">
-        <v>0</v>
-      </c>
-      <c r="L36" s="9">
-        <v>0</v>
-      </c>
-      <c r="M36" s="9">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L36" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="M36" s="7">
+        <v>1</v>
       </c>
       <c r="N36" s="9">
         <v>0</v>
       </c>
-      <c r="O36" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P36" s="9">
-        <v>-1</v>
+      <c r="O36" s="9">
+        <v>0</v>
+      </c>
+      <c r="P36" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q36" s="9">
         <v>-1</v>
@@ -1286,20 +1236,25 @@
       <c r="R36" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="37" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C37" s="20" t="s">
-        <v>56</v>
+      <c r="S36" s="9">
+        <v>-1</v>
+      </c>
+      <c r="T36" s="10"/>
+      <c r="U36" s="1"/>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C37" s="20" t="str">
+        <f>C36</f>
+        <v>2025 Final</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E37" s="9">
-        <v>0</v>
-      </c>
-      <c r="F37" s="15">
-        <f t="shared" si="0"/>
-        <v>5</v>
+      <c r="E37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>9</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>30</v>
@@ -1308,13 +1263,13 @@
         <v>30</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K37" s="9">
-        <v>0</v>
+      <c r="K37" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L37" s="9">
         <v>0</v>
@@ -1325,11 +1280,11 @@
       <c r="N37" s="9">
         <v>0</v>
       </c>
-      <c r="O37" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P37" s="9">
-        <v>-1</v>
+      <c r="O37" s="9">
+        <v>0</v>
+      </c>
+      <c r="P37" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q37" s="9">
         <v>-1</v>
@@ -1337,314 +1292,358 @@
       <c r="R37" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="38" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C38" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" s="20" t="s">
+      <c r="S37" s="9">
+        <v>-1</v>
+      </c>
+      <c r="T37" s="10"/>
+      <c r="U37" s="1"/>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C38" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="24">
+        <v>16</v>
+      </c>
+      <c r="G38" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H38" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="K38" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="L38" s="27">
+        <v>0</v>
+      </c>
+      <c r="M38" s="27">
+        <v>0</v>
+      </c>
+      <c r="N38" s="27">
+        <v>0</v>
+      </c>
+      <c r="O38" s="27">
+        <v>0</v>
+      </c>
+      <c r="P38" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q38" s="27">
+        <v>-1</v>
+      </c>
+      <c r="R38" s="27">
+        <v>-1</v>
+      </c>
+      <c r="S38" s="27">
+        <v>-1</v>
+      </c>
+      <c r="T38" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="U38" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="V38" s="22"/>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C39" s="20" t="str">
+        <f>C38</f>
+        <v>2025 Final</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L39" s="9">
+        <v>0</v>
+      </c>
+      <c r="M39" s="9">
+        <v>0</v>
+      </c>
+      <c r="N39" s="9">
+        <v>0</v>
+      </c>
+      <c r="O39" s="9">
+        <v>0</v>
+      </c>
+      <c r="P39" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R39" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S39" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C40" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="24">
+        <v>1</v>
+      </c>
+      <c r="G40" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H40" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="K40" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="L40" s="27">
+        <v>0</v>
+      </c>
+      <c r="M40" s="27">
+        <v>0</v>
+      </c>
+      <c r="N40" s="27">
+        <v>0</v>
+      </c>
+      <c r="O40" s="27">
+        <v>0</v>
+      </c>
+      <c r="P40" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q40" s="27">
+        <v>-1</v>
+      </c>
+      <c r="R40" s="27">
+        <v>-1</v>
+      </c>
+      <c r="S40" s="27">
+        <v>-1</v>
+      </c>
+      <c r="T40" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="U40" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="V40" s="22"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C41" s="20" t="str">
+        <f t="shared" ref="C41" si="0">C40</f>
+        <v>2025 Final</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="15">
+        <v>16</v>
+      </c>
+      <c r="G41" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="H41" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="I41" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="K41" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="L41" s="29">
+        <v>0</v>
+      </c>
+      <c r="M41" s="29">
+        <v>0</v>
+      </c>
+      <c r="N41" s="29">
+        <v>0</v>
+      </c>
+      <c r="O41" s="29">
+        <v>0</v>
+      </c>
+      <c r="P41" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q41" s="29">
+        <v>-1</v>
+      </c>
+      <c r="R41" s="29">
+        <v>-1</v>
+      </c>
+      <c r="S41" s="29">
+        <v>-1</v>
+      </c>
+      <c r="T41" s="31"/>
+      <c r="U41" s="31"/>
+      <c r="V41" s="31"/>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C42" s="20" t="str">
+        <f t="shared" ref="C42" si="1">C41</f>
+        <v>2025 Final</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L42" s="9">
+        <v>0</v>
+      </c>
+      <c r="M42" s="9">
+        <v>0</v>
+      </c>
+      <c r="N42" s="9">
+        <v>0</v>
+      </c>
+      <c r="O42" s="9">
+        <v>0</v>
+      </c>
+      <c r="P42" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q42" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R42" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S42" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C43" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="E38" s="9">
-        <v>0</v>
-      </c>
-      <c r="F38" s="15">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="9">
-        <v>0</v>
-      </c>
-      <c r="L38" s="9">
-        <v>0</v>
-      </c>
-      <c r="M38" s="9">
-        <v>0</v>
-      </c>
-      <c r="N38" s="9">
-        <v>0</v>
-      </c>
-      <c r="O38" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P38" s="9">
-        <v>-1</v>
-      </c>
-      <c r="Q38" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R38" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C39" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0</v>
-      </c>
-      <c r="F39" s="15">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="9">
-        <v>0</v>
-      </c>
-      <c r="L39" s="9">
-        <v>0</v>
-      </c>
-      <c r="M39" s="9">
-        <v>0</v>
-      </c>
-      <c r="N39" s="9">
-        <v>0</v>
-      </c>
-      <c r="O39" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P39" s="9">
-        <v>-1</v>
-      </c>
-      <c r="Q39" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R39" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C40" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0</v>
-      </c>
-      <c r="F40" s="15">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="9">
-        <v>0</v>
-      </c>
-      <c r="L40" s="9">
-        <v>0</v>
-      </c>
-      <c r="M40" s="9">
-        <v>0</v>
-      </c>
-      <c r="N40" s="9">
-        <v>0</v>
-      </c>
-      <c r="O40" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P40" s="9">
-        <v>-1</v>
-      </c>
-      <c r="Q40" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R40" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C41" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E41" s="9">
-        <v>0</v>
-      </c>
-      <c r="F41" s="15">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" s="9">
-        <v>0</v>
-      </c>
-      <c r="L41" s="9">
-        <v>0</v>
-      </c>
-      <c r="M41" s="9">
-        <v>0</v>
-      </c>
-      <c r="N41" s="9">
-        <v>0</v>
-      </c>
-      <c r="O41" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P41" s="9">
-        <v>-1</v>
-      </c>
-      <c r="Q41" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R41" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C42" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0</v>
-      </c>
-      <c r="F42" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K42" s="9">
-        <v>0</v>
-      </c>
-      <c r="L42" s="9">
-        <v>0</v>
-      </c>
-      <c r="M42" s="9">
-        <v>0</v>
-      </c>
-      <c r="N42" s="9">
-        <v>0</v>
-      </c>
-      <c r="O42" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P42" s="9">
-        <v>-1</v>
-      </c>
-      <c r="Q42" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R42" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C43" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E43" s="9">
-        <v>0</v>
-      </c>
-      <c r="F43" s="15">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="9">
-        <v>0</v>
-      </c>
-      <c r="L43" s="9">
-        <v>0</v>
-      </c>
-      <c r="M43" s="9">
-        <v>0</v>
-      </c>
-      <c r="N43" s="9">
-        <v>0</v>
-      </c>
-      <c r="O43" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P43" s="9">
-        <v>-1</v>
-      </c>
-      <c r="Q43" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R43" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="E43" s="23">
+        <v>0</v>
+      </c>
+      <c r="F43" s="24">
+        <v>1</v>
+      </c>
+      <c r="G43" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H43" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="I43" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="K43" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43" s="26">
+        <v>0.7</v>
+      </c>
+      <c r="M43" s="27">
+        <v>0</v>
+      </c>
+      <c r="N43" s="27">
+        <v>0</v>
+      </c>
+      <c r="O43" s="27">
+        <v>0</v>
+      </c>
+      <c r="P43" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q43" s="27">
+        <v>-1</v>
+      </c>
+      <c r="R43" s="27">
+        <v>-1</v>
+      </c>
+      <c r="S43" s="27">
+        <v>-1</v>
+      </c>
+      <c r="T43" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="U43" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="V43" s="22"/>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C44" s="20" t="s">
         <v>56</v>
       </c>
@@ -1655,8 +1654,8 @@
         <v>0</v>
       </c>
       <c r="F44" s="15">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>F43+1</f>
+        <v>2</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>30</v>
@@ -1668,10 +1667,10 @@
         <v>16</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L44" s="9">
         <v>0</v>
@@ -1682,11 +1681,11 @@
       <c r="N44" s="9">
         <v>0</v>
       </c>
-      <c r="O44" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P44" s="9">
-        <v>-1</v>
+      <c r="O44" s="9">
+        <v>0</v>
+      </c>
+      <c r="P44" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q44" s="9">
         <v>-1</v>
@@ -1694,8 +1693,11 @@
       <c r="R44" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="45" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S44" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C45" s="20" t="s">
         <v>56</v>
       </c>
@@ -1706,8 +1708,8 @@
         <v>0</v>
       </c>
       <c r="F45" s="15">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f t="shared" ref="F45:F58" si="2">F44+1</f>
+        <v>3</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>30</v>
@@ -1719,10 +1721,10 @@
         <v>17</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K45" s="9">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="L45" s="9">
         <v>0</v>
@@ -1733,11 +1735,11 @@
       <c r="N45" s="9">
         <v>0</v>
       </c>
-      <c r="O45" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P45" s="9">
-        <v>-1</v>
+      <c r="O45" s="9">
+        <v>0</v>
+      </c>
+      <c r="P45" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q45" s="9">
         <v>-1</v>
@@ -1745,8 +1747,11 @@
       <c r="R45" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="46" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S45" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C46" s="20" t="s">
         <v>56</v>
       </c>
@@ -1757,8 +1762,8 @@
         <v>0</v>
       </c>
       <c r="F46" s="15">
-        <f t="shared" si="0"/>
-        <v>14</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="G46" s="10" t="s">
         <v>30</v>
@@ -1770,10 +1775,10 @@
         <v>17</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K46" s="9">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="L46" s="9">
         <v>0</v>
@@ -1784,11 +1789,11 @@
       <c r="N46" s="9">
         <v>0</v>
       </c>
-      <c r="O46" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P46" s="9">
-        <v>-1</v>
+      <c r="O46" s="9">
+        <v>0</v>
+      </c>
+      <c r="P46" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q46" s="9">
         <v>-1</v>
@@ -1796,8 +1801,11 @@
       <c r="R46" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="47" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S46" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C47" s="20" t="s">
         <v>56</v>
       </c>
@@ -1808,8 +1816,8 @@
         <v>0</v>
       </c>
       <c r="F47" s="15">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>30</v>
@@ -1821,10 +1829,10 @@
         <v>16</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K47" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L47" s="9">
         <v>0</v>
@@ -1835,11 +1843,11 @@
       <c r="N47" s="9">
         <v>0</v>
       </c>
-      <c r="O47" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P47" s="9">
-        <v>-1</v>
+      <c r="O47" s="9">
+        <v>0</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q47" s="9">
         <v>-1</v>
@@ -1847,73 +1855,77 @@
       <c r="R47" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="48" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C48" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48" s="21" t="s">
+      <c r="S47" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C48" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E48" s="12">
-        <v>0</v>
-      </c>
-      <c r="F48" s="16">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="G48" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K48" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="L48" s="8">
-        <v>1</v>
-      </c>
-      <c r="M48" s="12">
-        <v>0</v>
-      </c>
-      <c r="N48" s="12">
-        <v>0</v>
-      </c>
-      <c r="O48" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="P48" s="12">
-        <v>-1</v>
-      </c>
-      <c r="Q48" s="12">
-        <v>-1</v>
-      </c>
-      <c r="R48" s="12">
-        <v>-1</v>
-      </c>
-      <c r="S48" s="3"/>
-      <c r="T48" s="3"/>
-      <c r="U48" s="3"/>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C49" t="s">
-        <v>56</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="E48" s="9">
+        <v>0</v>
+      </c>
+      <c r="F48" s="15">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L48" s="9">
+        <v>0</v>
+      </c>
+      <c r="M48" s="9">
+        <v>0</v>
+      </c>
+      <c r="N48" s="9">
+        <v>0</v>
+      </c>
+      <c r="O48" s="9">
+        <v>0</v>
+      </c>
+      <c r="P48" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q48" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R48" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S48" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C49" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>9</v>
+      <c r="E49" s="9">
+        <v>0</v>
       </c>
       <c r="F49" s="15">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
       <c r="G49" s="10" t="s">
         <v>30</v>
@@ -1925,10 +1937,10 @@
         <v>16</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K49" s="7">
-        <v>0.7</v>
+        <v>16</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L49" s="9">
         <v>0</v>
@@ -1939,11 +1951,11 @@
       <c r="N49" s="9">
         <v>0</v>
       </c>
-      <c r="O49" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P49" s="9">
-        <v>-1</v>
+      <c r="O49" s="9">
+        <v>0</v>
+      </c>
+      <c r="P49" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q49" s="9">
         <v>-1</v>
@@ -1951,26 +1963,23 @@
       <c r="R49" s="9">
         <v>-1</v>
       </c>
-      <c r="S49" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="T49" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S49" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C50" s="20" t="s">
         <v>56</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E50" s="9" t="s">
-        <v>9</v>
+      <c r="E50" s="9">
+        <v>0</v>
       </c>
       <c r="F50" s="15">
-        <f>F49+1</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>8</v>
       </c>
       <c r="G50" s="10" t="s">
         <v>30</v>
@@ -1982,10 +1991,10 @@
         <v>16</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K50" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L50" s="9">
         <v>0</v>
@@ -1996,11 +2005,11 @@
       <c r="N50" s="9">
         <v>0</v>
       </c>
-      <c r="O50" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P50" s="9">
-        <v>-1</v>
+      <c r="O50" s="9">
+        <v>0</v>
+      </c>
+      <c r="P50" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q50" s="9">
         <v>-1</v>
@@ -2008,20 +2017,23 @@
       <c r="R50" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S50" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C51" s="20" t="s">
         <v>56</v>
       </c>
       <c r="D51" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E51" s="9" t="s">
-        <v>9</v>
+      <c r="E51" s="9">
+        <v>0</v>
       </c>
       <c r="F51" s="15">
-        <f t="shared" ref="F51:F64" si="1">F50+1</f>
-        <v>3</v>
+        <f t="shared" si="2"/>
+        <v>9</v>
       </c>
       <c r="G51" s="10" t="s">
         <v>30</v>
@@ -2033,10 +2045,10 @@
         <v>16</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K51" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L51" s="9">
         <v>0</v>
@@ -2047,11 +2059,11 @@
       <c r="N51" s="9">
         <v>0</v>
       </c>
-      <c r="O51" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P51" s="9">
-        <v>-1</v>
+      <c r="O51" s="9">
+        <v>0</v>
+      </c>
+      <c r="P51" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q51" s="9">
         <v>-1</v>
@@ -2059,20 +2071,23 @@
       <c r="R51" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S51" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C52" s="20" t="s">
         <v>56</v>
       </c>
       <c r="D52" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E52" s="9" t="s">
-        <v>9</v>
+      <c r="E52" s="9">
+        <v>0</v>
       </c>
       <c r="F52" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>10</v>
       </c>
       <c r="G52" s="10" t="s">
         <v>30</v>
@@ -2084,10 +2099,10 @@
         <v>16</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K52" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L52" s="9">
         <v>0</v>
@@ -2098,11 +2113,11 @@
       <c r="N52" s="9">
         <v>0</v>
       </c>
-      <c r="O52" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P52" s="9">
-        <v>-1</v>
+      <c r="O52" s="9">
+        <v>0</v>
+      </c>
+      <c r="P52" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q52" s="9">
         <v>-1</v>
@@ -2110,20 +2125,23 @@
       <c r="R52" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S52" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C53" s="20" t="s">
         <v>56</v>
       </c>
       <c r="D53" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E53" s="9" t="s">
-        <v>9</v>
+      <c r="E53" s="9">
+        <v>0</v>
       </c>
       <c r="F53" s="15">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>11</v>
       </c>
       <c r="G53" s="10" t="s">
         <v>30</v>
@@ -2135,10 +2153,10 @@
         <v>16</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K53" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L53" s="9">
         <v>0</v>
@@ -2149,11 +2167,11 @@
       <c r="N53" s="9">
         <v>0</v>
       </c>
-      <c r="O53" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P53" s="9">
-        <v>-1</v>
+      <c r="O53" s="9">
+        <v>0</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q53" s="9">
         <v>-1</v>
@@ -2161,20 +2179,23 @@
       <c r="R53" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S53" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C54" s="20" t="s">
         <v>56</v>
       </c>
       <c r="D54" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E54" s="9" t="s">
-        <v>9</v>
+      <c r="E54" s="9">
+        <v>0</v>
       </c>
       <c r="F54" s="15">
-        <f t="shared" si="1"/>
-        <v>6</v>
+        <f t="shared" si="2"/>
+        <v>12</v>
       </c>
       <c r="G54" s="10" t="s">
         <v>30</v>
@@ -2186,10 +2207,10 @@
         <v>16</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K54" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L54" s="9">
         <v>0</v>
@@ -2200,11 +2221,11 @@
       <c r="N54" s="9">
         <v>0</v>
       </c>
-      <c r="O54" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P54" s="9">
-        <v>-1</v>
+      <c r="O54" s="9">
+        <v>0</v>
+      </c>
+      <c r="P54" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q54" s="9">
         <v>-1</v>
@@ -2212,20 +2233,23 @@
       <c r="R54" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S54" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C55" s="20" t="s">
         <v>56</v>
       </c>
       <c r="D55" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E55" s="9" t="s">
-        <v>9</v>
+      <c r="E55" s="9">
+        <v>0</v>
       </c>
       <c r="F55" s="15">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>13</v>
       </c>
       <c r="G55" s="10" t="s">
         <v>30</v>
@@ -2234,13 +2258,13 @@
         <v>30</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K55" s="9">
-        <v>0</v>
+      <c r="K55" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="L55" s="9">
         <v>0</v>
@@ -2251,11 +2275,11 @@
       <c r="N55" s="9">
         <v>0</v>
       </c>
-      <c r="O55" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P55" s="9">
-        <v>-1</v>
+      <c r="O55" s="9">
+        <v>0</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q55" s="9">
         <v>-1</v>
@@ -2263,20 +2287,23 @@
       <c r="R55" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S55" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C56" s="20" t="s">
         <v>56</v>
       </c>
       <c r="D56" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E56" s="9" t="s">
-        <v>9</v>
+      <c r="E56" s="9">
+        <v>0</v>
       </c>
       <c r="F56" s="15">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f t="shared" si="2"/>
+        <v>14</v>
       </c>
       <c r="G56" s="10" t="s">
         <v>30</v>
@@ -2285,13 +2312,13 @@
         <v>30</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K56" s="9">
-        <v>0</v>
+      <c r="K56" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="L56" s="9">
         <v>0</v>
@@ -2302,11 +2329,11 @@
       <c r="N56" s="9">
         <v>0</v>
       </c>
-      <c r="O56" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P56" s="9">
-        <v>-1</v>
+      <c r="O56" s="9">
+        <v>0</v>
+      </c>
+      <c r="P56" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q56" s="9">
         <v>-1</v>
@@ -2314,20 +2341,23 @@
       <c r="R56" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S56" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C57" s="20" t="s">
         <v>56</v>
       </c>
       <c r="D57" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E57" s="9" t="s">
-        <v>9</v>
+      <c r="E57" s="9">
+        <v>0</v>
       </c>
       <c r="F57" s="15">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>15</v>
       </c>
       <c r="G57" s="10" t="s">
         <v>30</v>
@@ -2339,10 +2369,10 @@
         <v>16</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K57" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L57" s="9">
         <v>0</v>
@@ -2353,11 +2383,11 @@
       <c r="N57" s="9">
         <v>0</v>
       </c>
-      <c r="O57" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P57" s="9">
-        <v>-1</v>
+      <c r="O57" s="9">
+        <v>0</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q57" s="9">
         <v>-1</v>
@@ -2365,71 +2395,79 @@
       <c r="R57" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C58" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D58" s="20" t="s">
+      <c r="S57" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C58" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="E58" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" s="15">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K58" s="9">
-        <v>0</v>
-      </c>
-      <c r="L58" s="9">
-        <v>0</v>
-      </c>
-      <c r="M58" s="9">
-        <v>0</v>
-      </c>
-      <c r="N58" s="9">
-        <v>0</v>
-      </c>
-      <c r="O58" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P58" s="9">
-        <v>-1</v>
-      </c>
-      <c r="Q58" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R58" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C59" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D59" s="20" t="s">
+      <c r="E58" s="12">
+        <v>0</v>
+      </c>
+      <c r="F58" s="16">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L58" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="M58" s="8">
+        <v>1</v>
+      </c>
+      <c r="N58" s="12">
+        <v>0</v>
+      </c>
+      <c r="O58" s="12">
+        <v>0</v>
+      </c>
+      <c r="P58" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q58" s="12">
+        <v>-1</v>
+      </c>
+      <c r="R58" s="12">
+        <v>-1</v>
+      </c>
+      <c r="S58" s="12">
+        <v>-1</v>
+      </c>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C59" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" t="s">
         <v>36</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="E59" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F59" s="15">
-        <f t="shared" si="1"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G59" s="10" t="s">
         <v>30</v>
@@ -2441,13 +2479,13 @@
         <v>16</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K59" s="9">
-        <v>0</v>
-      </c>
-      <c r="L59" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L59" s="7">
+        <v>0.7</v>
       </c>
       <c r="M59" s="9">
         <v>0</v>
@@ -2455,11 +2493,11 @@
       <c r="N59" s="9">
         <v>0</v>
       </c>
-      <c r="O59" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P59" s="9">
-        <v>-1</v>
+      <c r="O59" s="9">
+        <v>0</v>
+      </c>
+      <c r="P59" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q59" s="9">
         <v>-1</v>
@@ -2467,8 +2505,17 @@
       <c r="R59" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S59" s="9">
+        <v>-1</v>
+      </c>
+      <c r="T59" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="U59" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C60" s="20" t="s">
         <v>56</v>
       </c>
@@ -2479,8 +2526,8 @@
         <v>9</v>
       </c>
       <c r="F60" s="15">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f>F59+1</f>
+        <v>2</v>
       </c>
       <c r="G60" s="10" t="s">
         <v>30</v>
@@ -2492,10 +2539,10 @@
         <v>16</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K60" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L60" s="9">
         <v>0</v>
@@ -2506,11 +2553,11 @@
       <c r="N60" s="9">
         <v>0</v>
       </c>
-      <c r="O60" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P60" s="9">
-        <v>-1</v>
+      <c r="O60" s="9">
+        <v>0</v>
+      </c>
+      <c r="P60" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q60" s="9">
         <v>-1</v>
@@ -2518,8 +2565,11 @@
       <c r="R60" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S60" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C61" s="20" t="s">
         <v>56</v>
       </c>
@@ -2530,8 +2580,8 @@
         <v>9</v>
       </c>
       <c r="F61" s="15">
-        <f t="shared" si="1"/>
-        <v>13</v>
+        <f t="shared" ref="F61:F74" si="3">F60+1</f>
+        <v>3</v>
       </c>
       <c r="G61" s="10" t="s">
         <v>30</v>
@@ -2543,10 +2593,10 @@
         <v>16</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K61" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L61" s="9">
         <v>0</v>
@@ -2557,11 +2607,11 @@
       <c r="N61" s="9">
         <v>0</v>
       </c>
-      <c r="O61" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P61" s="9">
-        <v>-1</v>
+      <c r="O61" s="9">
+        <v>0</v>
+      </c>
+      <c r="P61" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q61" s="9">
         <v>-1</v>
@@ -2569,8 +2619,11 @@
       <c r="R61" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S61" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C62" s="20" t="s">
         <v>56</v>
       </c>
@@ -2581,8 +2634,8 @@
         <v>9</v>
       </c>
       <c r="F62" s="15">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>30</v>
@@ -2594,10 +2647,10 @@
         <v>16</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K62" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L62" s="9">
         <v>0</v>
@@ -2608,11 +2661,11 @@
       <c r="N62" s="9">
         <v>0</v>
       </c>
-      <c r="O62" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P62" s="9">
-        <v>-1</v>
+      <c r="O62" s="9">
+        <v>0</v>
+      </c>
+      <c r="P62" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q62" s="9">
         <v>-1</v>
@@ -2620,8 +2673,11 @@
       <c r="R62" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S62" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C63" s="20" t="s">
         <v>56</v>
       </c>
@@ -2632,8 +2688,8 @@
         <v>9</v>
       </c>
       <c r="F63" s="15">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="G63" s="10" t="s">
         <v>30</v>
@@ -2645,10 +2701,10 @@
         <v>16</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K63" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L63" s="9">
         <v>0</v>
@@ -2659,11 +2715,11 @@
       <c r="N63" s="9">
         <v>0</v>
       </c>
-      <c r="O63" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P63" s="9">
-        <v>-1</v>
+      <c r="O63" s="9">
+        <v>0</v>
+      </c>
+      <c r="P63" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q63" s="9">
         <v>-1</v>
@@ -2671,73 +2727,77 @@
       <c r="R63" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C64" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D64" s="21" t="s">
+      <c r="S63" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C64" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D64" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E64" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" s="16">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="G64" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H64" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I64" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K64" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="L64" s="8">
-        <v>1</v>
-      </c>
-      <c r="M64" s="12">
-        <v>0</v>
-      </c>
-      <c r="N64" s="12">
-        <v>0</v>
-      </c>
-      <c r="O64" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="P64" s="12">
-        <v>-1</v>
-      </c>
-      <c r="Q64" s="12">
-        <v>-1</v>
-      </c>
-      <c r="R64" s="12">
-        <v>-1</v>
-      </c>
-      <c r="S64" s="3"/>
-      <c r="T64" s="3"/>
-      <c r="U64" s="3"/>
-    </row>
-    <row r="65" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C65" t="s">
-        <v>56</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="E64" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="15">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L64" s="9">
+        <v>0</v>
+      </c>
+      <c r="M64" s="9">
+        <v>0</v>
+      </c>
+      <c r="N64" s="9">
+        <v>0</v>
+      </c>
+      <c r="O64" s="9">
+        <v>0</v>
+      </c>
+      <c r="P64" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q64" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R64" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S64" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C65" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D65" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E65" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F65" s="15">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="G65" s="10" t="s">
         <v>30</v>
@@ -2746,13 +2806,13 @@
         <v>30</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K65" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L65" s="9">
         <v>0</v>
@@ -2763,11 +2823,11 @@
       <c r="N65" s="9">
         <v>0</v>
       </c>
-      <c r="O65" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P65" s="9">
-        <v>-1</v>
+      <c r="O65" s="9">
+        <v>0</v>
+      </c>
+      <c r="P65" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q65" s="9">
         <v>-1</v>
@@ -2775,27 +2835,23 @@
       <c r="R65" s="9">
         <v>-1</v>
       </c>
-      <c r="S65" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="T65" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="66" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S65" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="66" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C66" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D66" s="9" t="str">
-        <f>D65</f>
-        <v>*</v>
+      <c r="D66" s="20" t="s">
+        <v>36</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F66" s="15">
-        <f>F65+1</f>
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>30</v>
@@ -2804,13 +2860,13 @@
         <v>30</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K66" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L66" s="9">
         <v>0</v>
@@ -2821,11 +2877,11 @@
       <c r="N66" s="9">
         <v>0</v>
       </c>
-      <c r="O66" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P66" s="9">
-        <v>-1</v>
+      <c r="O66" s="9">
+        <v>0</v>
+      </c>
+      <c r="P66" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q66" s="9">
         <v>-1</v>
@@ -2833,21 +2889,23 @@
       <c r="R66" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="67" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S66" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="67" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C67" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D67" s="9" t="str">
-        <f t="shared" ref="D67:D80" si="2">D66</f>
-        <v>*</v>
+      <c r="D67" s="20" t="s">
+        <v>36</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F67" s="15">
-        <f t="shared" ref="F67:F80" si="3">F66+1</f>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="G67" s="10" t="s">
         <v>30</v>
@@ -2856,13 +2914,13 @@
         <v>30</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K67" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L67" s="9">
         <v>0</v>
@@ -2873,11 +2931,11 @@
       <c r="N67" s="9">
         <v>0</v>
       </c>
-      <c r="O67" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P67" s="9">
-        <v>-1</v>
+      <c r="O67" s="9">
+        <v>0</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q67" s="9">
         <v>-1</v>
@@ -2885,21 +2943,23 @@
       <c r="R67" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="68" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S67" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="68" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C68" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D68" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>*</v>
+      <c r="D68" s="20" t="s">
+        <v>36</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G68" s="10" t="s">
         <v>30</v>
@@ -2908,13 +2968,13 @@
         <v>30</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K68" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L68" s="9">
         <v>0</v>
@@ -2925,11 +2985,11 @@
       <c r="N68" s="9">
         <v>0</v>
       </c>
-      <c r="O68" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="P68" s="19">
-        <v>0.4</v>
+      <c r="O68" s="9">
+        <v>0</v>
+      </c>
+      <c r="P68" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q68" s="9">
         <v>-1</v>
@@ -2937,21 +2997,23 @@
       <c r="R68" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="69" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S68" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="69" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C69" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D69" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>*</v>
+      <c r="D69" s="20" t="s">
+        <v>36</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F69" s="15">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G69" s="10" t="s">
         <v>30</v>
@@ -2960,13 +3022,13 @@
         <v>30</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K69" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L69" s="9">
         <v>0</v>
@@ -2977,11 +3039,11 @@
       <c r="N69" s="9">
         <v>0</v>
       </c>
-      <c r="O69" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="P69" s="19">
-        <v>0.4</v>
+      <c r="O69" s="9">
+        <v>0</v>
+      </c>
+      <c r="P69" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q69" s="9">
         <v>-1</v>
@@ -2989,21 +3051,23 @@
       <c r="R69" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="70" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S69" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="70" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C70" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D70" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>*</v>
+      <c r="D70" s="20" t="s">
+        <v>36</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F70" s="15">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G70" s="10" t="s">
         <v>30</v>
@@ -3012,13 +3076,13 @@
         <v>30</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K70" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L70" s="9">
         <v>0</v>
@@ -3029,11 +3093,11 @@
       <c r="N70" s="9">
         <v>0</v>
       </c>
-      <c r="O70" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="P70" s="19">
-        <v>0.4</v>
+      <c r="O70" s="9">
+        <v>0</v>
+      </c>
+      <c r="P70" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q70" s="9">
         <v>-1</v>
@@ -3041,21 +3105,23 @@
       <c r="R70" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="71" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S70" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="71" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C71" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D71" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>*</v>
+      <c r="D71" s="20" t="s">
+        <v>36</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G71" s="10" t="s">
         <v>30</v>
@@ -3064,13 +3130,13 @@
         <v>30</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K71" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L71" s="9">
         <v>0</v>
@@ -3081,11 +3147,11 @@
       <c r="N71" s="9">
         <v>0</v>
       </c>
-      <c r="O71" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="P71" s="19">
-        <v>0.4</v>
+      <c r="O71" s="9">
+        <v>0</v>
+      </c>
+      <c r="P71" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q71" s="9">
         <v>-1</v>
@@ -3093,21 +3159,23 @@
       <c r="R71" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="72" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S71" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="72" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C72" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D72" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>*</v>
+      <c r="D72" s="20" t="s">
+        <v>36</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G72" s="10" t="s">
         <v>30</v>
@@ -3116,13 +3184,13 @@
         <v>30</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K72" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L72" s="9">
         <v>0</v>
@@ -3133,11 +3201,11 @@
       <c r="N72" s="9">
         <v>0</v>
       </c>
-      <c r="O72" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="P72" s="19">
-        <v>0.4</v>
+      <c r="O72" s="9">
+        <v>0</v>
+      </c>
+      <c r="P72" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="Q72" s="9">
         <v>-1</v>
@@ -3145,21 +3213,23 @@
       <c r="R72" s="9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="73" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="S72" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="73" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C73" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D73" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>*</v>
+      <c r="D73" s="20" t="s">
+        <v>36</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G73" s="10" t="s">
         <v>30</v>
@@ -3168,13 +3238,13 @@
         <v>30</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K73" s="9">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L73" s="9">
         <v>0</v>
@@ -3185,449 +3255,1016 @@
       <c r="N73" s="9">
         <v>0</v>
       </c>
-      <c r="O73" s="19" t="s">
+      <c r="O73" s="9">
+        <v>0</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q73" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R73" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S73" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="74" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C74" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="16">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L74" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="M74" s="8">
+        <v>1</v>
+      </c>
+      <c r="N74" s="12">
+        <v>0</v>
+      </c>
+      <c r="O74" s="12">
+        <v>0</v>
+      </c>
+      <c r="P74" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q74" s="12">
+        <v>-1</v>
+      </c>
+      <c r="R74" s="12">
+        <v>-1</v>
+      </c>
+      <c r="S74" s="12">
+        <v>-1</v>
+      </c>
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+    </row>
+    <row r="75" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C75" t="s">
+        <v>56</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="15">
+        <v>1</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K75" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L75" s="9">
+        <v>0</v>
+      </c>
+      <c r="M75" s="9">
+        <v>0</v>
+      </c>
+      <c r="N75" s="9">
+        <v>0</v>
+      </c>
+      <c r="O75" s="9">
+        <v>0</v>
+      </c>
+      <c r="P75" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q75" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R75" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S75" s="9">
+        <v>-1</v>
+      </c>
+      <c r="T75" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="U75" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="76" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C76" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D76" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" s="15">
+        <f>F75+1</f>
+        <v>2</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K76" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L76" s="9">
+        <v>0</v>
+      </c>
+      <c r="M76" s="9">
+        <v>0</v>
+      </c>
+      <c r="N76" s="9">
+        <v>0</v>
+      </c>
+      <c r="O76" s="9">
+        <v>0</v>
+      </c>
+      <c r="P76" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q76" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R76" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S76" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="77" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C77" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D77" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" s="15">
+        <f t="shared" ref="F77:F90" si="4">F76+1</f>
+        <v>3</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K77" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L77" s="9">
+        <v>0</v>
+      </c>
+      <c r="M77" s="9">
+        <v>0</v>
+      </c>
+      <c r="N77" s="9">
+        <v>0</v>
+      </c>
+      <c r="O77" s="9">
+        <v>0</v>
+      </c>
+      <c r="P77" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q77" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R77" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S77" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="78" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C78" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D78" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" s="15">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K78" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L78" s="9">
+        <v>0</v>
+      </c>
+      <c r="M78" s="9">
+        <v>0</v>
+      </c>
+      <c r="N78" s="9">
+        <v>0</v>
+      </c>
+      <c r="O78" s="9">
+        <v>0</v>
+      </c>
+      <c r="P78" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="P73" s="19">
+      <c r="Q78" s="19">
         <v>0.4</v>
       </c>
-      <c r="Q73" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R73" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="74" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C74" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D74" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>*</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" s="15">
-        <f t="shared" si="3"/>
+      <c r="R78" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S78" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="79" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C79" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D79" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" s="15">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K79" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L79" s="9">
+        <v>0</v>
+      </c>
+      <c r="M79" s="9">
+        <v>0</v>
+      </c>
+      <c r="N79" s="9">
+        <v>0</v>
+      </c>
+      <c r="O79" s="9">
+        <v>0</v>
+      </c>
+      <c r="P79" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q79" s="19">
+        <v>0.4</v>
+      </c>
+      <c r="R79" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S79" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="80" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C80" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D80" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" s="15">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K80" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L80" s="9">
+        <v>0</v>
+      </c>
+      <c r="M80" s="9">
+        <v>0</v>
+      </c>
+      <c r="N80" s="9">
+        <v>0</v>
+      </c>
+      <c r="O80" s="9">
+        <v>0</v>
+      </c>
+      <c r="P80" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q80" s="19">
+        <v>0.4</v>
+      </c>
+      <c r="R80" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S80" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="81" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C81" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D81" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" s="15">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K81" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L81" s="9">
+        <v>0</v>
+      </c>
+      <c r="M81" s="9">
+        <v>0</v>
+      </c>
+      <c r="N81" s="9">
+        <v>0</v>
+      </c>
+      <c r="O81" s="9">
+        <v>0</v>
+      </c>
+      <c r="P81" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q81" s="19">
+        <v>0.4</v>
+      </c>
+      <c r="R81" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S81" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="82" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C82" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D82" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" s="15">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K82" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L82" s="9">
+        <v>0</v>
+      </c>
+      <c r="M82" s="9">
+        <v>0</v>
+      </c>
+      <c r="N82" s="9">
+        <v>0</v>
+      </c>
+      <c r="O82" s="9">
+        <v>0</v>
+      </c>
+      <c r="P82" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q82" s="19">
+        <v>0.4</v>
+      </c>
+      <c r="R82" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S82" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="83" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C83" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D83" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="15">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K83" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L83" s="9">
+        <v>0</v>
+      </c>
+      <c r="M83" s="9">
+        <v>0</v>
+      </c>
+      <c r="N83" s="9">
+        <v>0</v>
+      </c>
+      <c r="O83" s="9">
+        <v>0</v>
+      </c>
+      <c r="P83" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q83" s="19">
+        <v>0.4</v>
+      </c>
+      <c r="R83" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S83" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="84" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C84" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D84" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="15">
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="G74" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H74" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K74" s="9">
-        <v>0</v>
-      </c>
-      <c r="L74" s="9">
-        <v>0</v>
-      </c>
-      <c r="M74" s="9">
-        <v>0</v>
-      </c>
-      <c r="N74" s="9">
-        <v>0</v>
-      </c>
-      <c r="O74" s="19" t="s">
+      <c r="G84" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K84" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L84" s="9">
+        <v>0</v>
+      </c>
+      <c r="M84" s="9">
+        <v>0</v>
+      </c>
+      <c r="N84" s="9">
+        <v>0</v>
+      </c>
+      <c r="O84" s="9">
+        <v>0</v>
+      </c>
+      <c r="P84" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="P74" s="19">
+      <c r="Q84" s="19">
         <v>0.4</v>
       </c>
-      <c r="Q74" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R74" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="75" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C75" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D75" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>*</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="15">
-        <f t="shared" si="3"/>
+      <c r="R84" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S84" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="85" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C85" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D85" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" s="15">
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="G75" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K75" s="9">
-        <v>0</v>
-      </c>
-      <c r="L75" s="9">
-        <v>0</v>
-      </c>
-      <c r="M75" s="9">
-        <v>0</v>
-      </c>
-      <c r="N75" s="9">
-        <v>0</v>
-      </c>
-      <c r="O75" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P75" s="9">
-        <v>-1</v>
-      </c>
-      <c r="Q75" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R75" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="76" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C76" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D76" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>*</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" s="15">
-        <f t="shared" si="3"/>
+      <c r="G85" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K85" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L85" s="9">
+        <v>0</v>
+      </c>
+      <c r="M85" s="9">
+        <v>0</v>
+      </c>
+      <c r="N85" s="9">
+        <v>0</v>
+      </c>
+      <c r="O85" s="9">
+        <v>0</v>
+      </c>
+      <c r="P85" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q85" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R85" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S85" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="86" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C86" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D86" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="15">
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="G76" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K76" s="9">
-        <v>0</v>
-      </c>
-      <c r="L76" s="9">
-        <v>0</v>
-      </c>
-      <c r="M76" s="9">
-        <v>0</v>
-      </c>
-      <c r="N76" s="9">
-        <v>0</v>
-      </c>
-      <c r="O76" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P76" s="9">
-        <v>-1</v>
-      </c>
-      <c r="Q76" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R76" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="77" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C77" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D77" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>*</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" s="15">
-        <f t="shared" si="3"/>
+      <c r="G86" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K86" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L86" s="9">
+        <v>0</v>
+      </c>
+      <c r="M86" s="9">
+        <v>0</v>
+      </c>
+      <c r="N86" s="9">
+        <v>0</v>
+      </c>
+      <c r="O86" s="9">
+        <v>0</v>
+      </c>
+      <c r="P86" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q86" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R86" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S86" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="87" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C87" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D87" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" s="15">
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="G77" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K77" s="9">
-        <v>0</v>
-      </c>
-      <c r="L77" s="9">
-        <v>0</v>
-      </c>
-      <c r="M77" s="9">
-        <v>0</v>
-      </c>
-      <c r="N77" s="9">
-        <v>0</v>
-      </c>
-      <c r="O77" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P77" s="9">
-        <v>-1</v>
-      </c>
-      <c r="Q77" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R77" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="78" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C78" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D78" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>*</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" s="15">
-        <f t="shared" si="3"/>
+      <c r="G87" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K87" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L87" s="9">
+        <v>0</v>
+      </c>
+      <c r="M87" s="9">
+        <v>0</v>
+      </c>
+      <c r="N87" s="9">
+        <v>0</v>
+      </c>
+      <c r="O87" s="9">
+        <v>0</v>
+      </c>
+      <c r="P87" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q87" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R87" s="9">
+        <v>-1</v>
+      </c>
+      <c r="S87" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C88" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D88" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" s="15">
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="G78" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K78" s="9">
-        <v>0</v>
-      </c>
-      <c r="L78" s="9">
-        <v>0</v>
-      </c>
-      <c r="M78" s="9">
-        <v>0</v>
-      </c>
-      <c r="N78" s="9">
-        <v>0</v>
-      </c>
-      <c r="O78" s="19" t="s">
+      <c r="G88" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K88" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L88" s="9">
+        <v>0</v>
+      </c>
+      <c r="M88" s="9">
+        <v>0</v>
+      </c>
+      <c r="N88" s="9">
+        <v>0</v>
+      </c>
+      <c r="O88" s="9">
+        <v>0</v>
+      </c>
+      <c r="P88" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="P78" s="19">
+      <c r="Q88" s="19">
         <v>0.6</v>
       </c>
-      <c r="Q78" s="19">
+      <c r="R88" s="19">
         <v>67</v>
       </c>
-      <c r="R78" s="19">
+      <c r="S88" s="19">
         <v>72</v>
       </c>
     </row>
-    <row r="79" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C79" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D79" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>*</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79" s="15">
-        <f t="shared" si="3"/>
+    <row r="89" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C89" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D89" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" s="15">
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="G79" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K79" s="9">
-        <v>0</v>
-      </c>
-      <c r="L79" s="9">
-        <v>0</v>
-      </c>
-      <c r="M79" s="9">
-        <v>0</v>
-      </c>
-      <c r="N79" s="9">
-        <v>0</v>
-      </c>
-      <c r="O79" s="19" t="s">
+      <c r="G89" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K89" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L89" s="9">
+        <v>0</v>
+      </c>
+      <c r="M89" s="9">
+        <v>0</v>
+      </c>
+      <c r="N89" s="9">
+        <v>0</v>
+      </c>
+      <c r="O89" s="9">
+        <v>0</v>
+      </c>
+      <c r="P89" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="P79" s="19">
+      <c r="Q89" s="19">
         <v>0.6</v>
       </c>
-      <c r="Q79" s="19">
+      <c r="R89" s="19">
         <v>67</v>
       </c>
-      <c r="R79" s="19">
+      <c r="S89" s="19">
         <v>72</v>
       </c>
     </row>
-    <row r="80" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C80" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D80" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>*</v>
-      </c>
-      <c r="E80" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" s="16">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-      <c r="G80" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H80" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I80" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="K80" s="12">
-        <v>0</v>
-      </c>
-      <c r="L80" s="12">
-        <v>0</v>
-      </c>
-      <c r="M80" s="12">
-        <v>0</v>
-      </c>
-      <c r="N80" s="12">
-        <v>0</v>
-      </c>
-      <c r="O80" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="P80" s="12">
-        <v>-1</v>
-      </c>
-      <c r="Q80" s="12">
-        <v>-1</v>
-      </c>
-      <c r="R80" s="12">
-        <v>-1</v>
-      </c>
-      <c r="S80" s="3"/>
-      <c r="T80" s="3"/>
-      <c r="U80" s="3"/>
-    </row>
-    <row r="81" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C81" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E81" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F81" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="G81" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H81" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="I81" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="J81" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="K81" s="13">
-        <v>0</v>
-      </c>
-      <c r="L81" s="13">
-        <v>0</v>
-      </c>
-      <c r="M81" s="13">
-        <v>0</v>
-      </c>
-      <c r="N81" s="13">
-        <v>0</v>
-      </c>
-      <c r="O81" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="P81" s="13">
-        <v>-1</v>
-      </c>
-      <c r="Q81" s="13">
-        <v>-1</v>
-      </c>
-      <c r="R81" s="13">
-        <v>-1</v>
-      </c>
-      <c r="S81" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="T81" s="14" t="s">
+    <row r="90" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C90" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D90" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" s="16">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="G90" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H90" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K90" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L90" s="12">
+        <v>0</v>
+      </c>
+      <c r="M90" s="12">
+        <v>0</v>
+      </c>
+      <c r="N90" s="12">
+        <v>0</v>
+      </c>
+      <c r="O90" s="12">
+        <v>0</v>
+      </c>
+      <c r="P90" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q90" s="12">
+        <v>-1</v>
+      </c>
+      <c r="R90" s="12">
+        <v>-1</v>
+      </c>
+      <c r="S90" s="12">
+        <v>-1</v>
+      </c>
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C91" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G91" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H91" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I91" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J91" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="K91" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L91" s="13">
+        <v>0</v>
+      </c>
+      <c r="M91" s="13">
+        <v>0</v>
+      </c>
+      <c r="N91" s="13">
+        <v>0</v>
+      </c>
+      <c r="O91" s="13">
+        <v>0</v>
+      </c>
+      <c r="P91" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q91" s="13">
+        <v>-1</v>
+      </c>
+      <c r="R91" s="13">
+        <v>-1</v>
+      </c>
+      <c r="S91" s="13">
+        <v>-1</v>
+      </c>
+      <c r="T91" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="U91" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="82" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B82" t="s">
+    <row r="92" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>